--- a/sources/bryan_step5.xlsx
+++ b/sources/bryan_step5.xlsx
@@ -722,6 +722,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>74993c60-9c25-4ff3-b3fa-f1296b65505c</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>74993c60-9c25-4ff3-b3fa-f1296b65505c</t>
@@ -769,6 +774,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>09ebf217-6f8c-49a1-9120-b6d903c7cee0</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>09ebf217-6f8c-49a1-9120-b6d903c7cee0</t>
@@ -814,6 +824,11 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>e28da776-8eb0-403d-bcb0-31b6cdece7b8</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -6087,6 +6102,11 @@
           <t>hmmmhhhhmh</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>1e24fe73-69af-4506-9a4b-0118515b9e02</t>
+        </is>
+      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>1e24fe73-69af-4506-9a4b-0118515b9e02</t>
@@ -6119,6 +6139,11 @@
           <t>hmmmhhhm</t>
         </is>
       </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>ef6f4e30-fc93-476d-aa40-bed23e6e262d</t>
+        </is>
+      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>ef6f4e30-fc93-476d-aa40-bed23e6e262d</t>
@@ -6149,6 +6174,11 @@
       <c r="K110" t="inlineStr">
         <is>
           <t>hmmmhhmh</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>f4a77540-d285-4628-a209-f8f0a4fbebf3</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">

--- a/sources/bryan_step5.xlsx
+++ b/sources/bryan_step5.xlsx
@@ -3025,6 +3025,11 @@
           <t>– &lt;2&lt;1~u</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>&lt;2&lt;1~d</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>– Side Step Lair's Dance</t>
@@ -4034,6 +4039,11 @@
           <t>– u</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
           <t>– Side Step Mach</t>
@@ -4282,6 +4292,11 @@
       <c r="A73" t="inlineStr">
         <is>
           <t>– ~f+2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>~b+2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
